--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_pb_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_pb_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3962,7 +3962,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6509,7 +6509,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7152,7 +7152,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7245,7 +7245,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7431,7 +7431,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9207,7 +9207,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9595,7 +9595,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10735,7 +10735,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10925,7 +10925,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12057,7 +12057,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12150,7 +12150,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>21-01-2021 08:30</t>
+          <t>2021-01-21 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12336,7 +12336,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12720,7 +12720,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12813,7 +12813,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>07-03-2021 08:30</t>
+          <t>2021-07-03 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14640,7 +14640,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14826,7 +14826,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14919,7 +14919,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15117,7 +15117,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15303,7 +15303,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15582,7 +15582,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15675,7 +15675,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15861,7 +15861,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15954,7 +15954,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -16043,7 +16043,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16581,7 +16581,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16674,7 +16674,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -16860,7 +16860,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -16953,7 +16953,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17046,7 +17046,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17139,7 +17139,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17232,7 +17232,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17418,7 +17418,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17511,7 +17511,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17697,7 +17697,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -17883,7 +17883,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18069,7 +18069,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18255,7 +18255,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18348,7 +18348,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18627,7 +18627,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18720,7 +18720,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -18813,7 +18813,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19282,7 +19282,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19375,7 +19375,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -19842,7 +19842,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -19931,7 +19931,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20376,7 +20376,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20554,7 +20554,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20643,7 +20643,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -20821,7 +20821,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -20910,7 +20910,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21003,7 +21003,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21189,7 +21189,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21282,7 +21282,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21375,7 +21375,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21561,7 +21561,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -21933,7 +21933,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22026,7 +22026,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22115,7 +22115,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22293,7 +22293,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22382,7 +22382,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22471,7 +22471,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22560,7 +22560,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -22831,7 +22831,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23017,7 +23017,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23195,7 +23195,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23377,7 +23377,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23563,7 +23563,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23656,7 +23656,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -23755,7 +23755,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -23953,7 +23953,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24042,7 +24042,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24131,7 +24131,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24309,7 +24309,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24406,7 +24406,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -24998,7 +24998,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
